--- a/Mantenimiento/excels/LIMA-LIMA-SAN_JUAN_DE_MIRAFLORES.xlsx
+++ b/Mantenimiento/excels/LIMA-LIMA-SAN_JUAN_DE_MIRAFLORES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,6 @@
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -508,7 +503,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -536,11 +531,6 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -560,7 +550,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,11 +578,6 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -612,7 +597,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -640,11 +625,6 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -664,7 +644,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -692,11 +672,6 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -716,7 +691,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -744,11 +719,6 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -768,7 +738,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -796,11 +766,6 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -820,7 +785,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -848,11 +813,6 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -872,7 +832,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -900,11 +860,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -924,7 +879,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -952,11 +907,6 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -976,7 +926,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1004,11 +954,6 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1028,7 +973,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1056,11 +1001,6 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1080,7 +1020,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1108,11 +1048,6 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1132,7 +1067,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1160,11 +1095,6 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1184,7 +1114,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1212,11 +1142,6 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1236,7 +1161,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1264,11 +1189,6 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1288,7 +1208,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1316,11 +1236,6 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1340,7 +1255,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1368,11 +1283,6 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1392,38 +1302,33 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>329969</t>
+          <t>329851</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JULIO CESAR ESCOBAR</t>
+          <t>7099 HECTOR PRETELL / 7099 HECTOR PRETELL CARBONELL</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>-12.16274</v>
+        <v>-12.17726</v>
       </c>
       <c r="H19" t="n">
-        <v>-76.9744</v>
+        <v>-76.96907</v>
       </c>
       <c r="I19" t="n">
-        <v>756</v>
+        <v>646</v>
       </c>
       <c r="J19" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
     <row r="20">
@@ -1444,38 +1349,33 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>330171</t>
+          <t>329969</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FERMIN TANGUIS</t>
+          <t>JULIO CESAR ESCOBAR</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>-12.1553</v>
+        <v>-12.16274</v>
       </c>
       <c r="H20" t="n">
-        <v>-76.97698</v>
+        <v>-76.9744</v>
       </c>
       <c r="I20" t="n">
-        <v>864</v>
+        <v>756</v>
       </c>
       <c r="J20" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
     <row r="21">
@@ -1496,38 +1396,33 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>330208</t>
+          <t>330171</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ISAAC NEWTON</t>
+          <t>FERMIN TANGUIS</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-12.18218</v>
+        <v>-12.1553</v>
       </c>
       <c r="H21" t="n">
-        <v>-76.97882</v>
+        <v>-76.97698</v>
       </c>
       <c r="I21" t="n">
-        <v>339</v>
+        <v>864</v>
       </c>
       <c r="J21" t="n">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
     <row r="22">
@@ -1548,38 +1443,33 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>330350</t>
+          <t>330208</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MARY'S CHILDREN SCHOOL</t>
+          <t>ISAAC NEWTON</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-12.16094</v>
+        <v>-12.18218</v>
       </c>
       <c r="H22" t="n">
-        <v>-76.96305</v>
+        <v>-76.97882</v>
       </c>
       <c r="I22" t="n">
-        <v>179</v>
+        <v>339</v>
       </c>
       <c r="J22" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
     <row r="23">
@@ -1600,38 +1490,33 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>331439</t>
+          <t>330350</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AMERICA SIGLO XXI</t>
+          <t>MARY'S CHILDREN SCHOOL</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>-12.18635</v>
+        <v>-12.16094</v>
       </c>
       <c r="H23" t="n">
-        <v>-76.97633</v>
+        <v>-76.96305</v>
       </c>
       <c r="I23" t="n">
-        <v>517</v>
+        <v>179</v>
       </c>
       <c r="J23" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
     <row r="24">
@@ -1652,38 +1537,33 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>331694</t>
+          <t>331439</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HEROES DEL PACIFICO</t>
+          <t>AMERICA SIGLO XXI</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-12.17175</v>
+        <v>-12.18635</v>
       </c>
       <c r="H24" t="n">
-        <v>-76.96933</v>
+        <v>-76.97633</v>
       </c>
       <c r="I24" t="n">
-        <v>370</v>
+        <v>517</v>
       </c>
       <c r="J24" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
     <row r="25">
@@ -1704,38 +1584,33 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>332132</t>
+          <t>331694</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>LEONARD EULER</t>
+          <t>HEROES DEL PACIFICO</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-12.16805</v>
+        <v>-12.17175</v>
       </c>
       <c r="H25" t="n">
-        <v>-76.97689</v>
+        <v>-76.96933</v>
       </c>
       <c r="I25" t="n">
-        <v>222</v>
+        <v>370</v>
       </c>
       <c r="J25" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
     <row r="26">
@@ -1756,38 +1631,80 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_MIRAFLORES</t>
+          <t>SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>332132</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>LEONARD EULER</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>-12.16805</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-76.97689</v>
+      </c>
+      <c r="I26" t="n">
+        <v>222</v>
+      </c>
+      <c r="J26" t="n">
+        <v>12</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>150133</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>614443</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>TALENTOS KIDS</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="G27" t="n">
         <v>-12.17971</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H27" t="n">
         <v>-76.98159</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I27" t="n">
         <v>193</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J27" t="n">
         <v>11</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="K27" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Mantenimiento/excels/LIMA-LIMA-SAN_JUAN_DE_MIRAFLORES.xlsx
+++ b/Mantenimiento/excels/LIMA-LIMA-SAN_JUAN_DE_MIRAFLORES.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,61 +413,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
@@ -516,20 +504,30 @@
           <t>513 NIÑOS DE MARIA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.16988</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-76.97503</v>
-      </c>
-      <c r="I2" t="n">
-        <v>268</v>
-      </c>
-      <c r="J2" t="n">
-        <v>13</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.16988</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-76.97503</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -563,20 +561,30 @@
           <t>514 EL CARMEN</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.16368</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-76.97778</v>
-      </c>
-      <c r="I3" t="n">
-        <v>421</v>
-      </c>
-      <c r="J3" t="n">
-        <v>17</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.16368</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-76.97778</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -602,28 +610,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>329238</t>
+          <t>329295</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>530 VIRGEN DE FATIMA</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>-12.15953</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-76.96722</v>
-      </c>
-      <c r="I4" t="n">
-        <v>514</v>
-      </c>
-      <c r="J4" t="n">
-        <v>21</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+          <t>559 SAGRADO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.17768</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-76.97801</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -649,28 +667,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>329295</t>
+          <t>329304</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>559 SAGRADO CORAZON DE JESUS</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>-12.17768</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-76.97801</v>
-      </c>
-      <c r="I5" t="n">
-        <v>204</v>
-      </c>
-      <c r="J5" t="n">
-        <v>9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+          <t>623 / 7101</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.18447</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-76.97897</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1067</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -696,28 +724,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>329304</t>
+          <t>329337</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>623 / 7101</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>-12.18447</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-76.97897</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1067</v>
-      </c>
-      <c r="J6" t="n">
-        <v>52</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+          <t>627 / 7212</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.17348</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-76.96406</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -743,28 +781,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>329337</t>
+          <t>329342</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>627 / 7212</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>-12.17348</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-76.96406</v>
-      </c>
-      <c r="I7" t="n">
-        <v>468</v>
-      </c>
-      <c r="J7" t="n">
-        <v>20</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+          <t>629-6034 CESAR CARBONEL RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.14525</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-76.9757</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -790,28 +838,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>329342</t>
+          <t>329399</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>629-6034 CESAR CARBONEL RODRIGUEZ</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>-12.14525</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-76.9757</v>
-      </c>
-      <c r="I8" t="n">
-        <v>674</v>
-      </c>
-      <c r="J8" t="n">
-        <v>33</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+          <t>635 EL UNIVERSO</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.18626</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-76.95811</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -837,28 +895,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>329399</t>
+          <t>329417</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>635 EL UNIVERSO</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>-12.18626</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-76.95811</v>
-      </c>
-      <c r="I9" t="n">
-        <v>238</v>
-      </c>
-      <c r="J9" t="n">
-        <v>11</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+          <t>637 VALLE SHARON</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.17238</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-76.97072</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -884,28 +952,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>329417</t>
+          <t>329484</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>637 VALLE SHARON</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>-12.17238</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-76.97072</v>
-      </c>
-      <c r="I10" t="n">
-        <v>447</v>
-      </c>
-      <c r="J10" t="n">
-        <v>20</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+          <t>7223 MIGUEL COLINA MARIE</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.15372</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-76.9797</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -931,28 +1009,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>329484</t>
+          <t>329506</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>7223 MIGUEL COLINA MARIE</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>-12.15372</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-76.97969999999999</v>
-      </c>
-      <c r="I11" t="n">
-        <v>290</v>
-      </c>
-      <c r="J11" t="n">
-        <v>11</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+          <t>652 13 LOS TREBOLITOS</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.17753</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-76.96367</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -978,28 +1066,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>329506</t>
+          <t>329686</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>652 13 LOS TREBOLITOS</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>-12.17753</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-76.96366999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>193</v>
-      </c>
-      <c r="J12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+          <t>6096 ANTONIO RAIMONDI</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.16712</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-76.96474</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>797</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1025,28 +1123,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>329686</t>
+          <t>329747</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6096 ANTONIO RAIMONDI</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>-12.16712</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-76.96474000000001</v>
-      </c>
-      <c r="I13" t="n">
-        <v>797</v>
-      </c>
-      <c r="J13" t="n">
-        <v>37</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+          <t>7061 LOS HEROES DE SAN JUAN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.15593</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-76.97544</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1282</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1072,28 +1180,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>329747</t>
+          <t>329752</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7061 LOS HEROES DE SAN JUAN</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>-12.15593</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-76.97544000000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1282</v>
-      </c>
-      <c r="J14" t="n">
-        <v>59</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+          <t>7062 NACIONES UNIDAS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.15619</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-76.97483</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1651</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1119,28 +1237,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>329752</t>
+          <t>329785</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>7062 NACIONES UNIDAS</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>-12.15619</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-76.97483</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1651</v>
-      </c>
-      <c r="J15" t="n">
-        <v>84</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+          <t>7069 CESAR VALLEJO</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.15099</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-76.97448</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1516</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1166,28 +1294,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>329785</t>
+          <t>329813</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>7069 CESAR VALLEJO</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>-12.15099</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-76.97448</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1516</v>
-      </c>
-      <c r="J16" t="n">
-        <v>74</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+          <t>7081 JOSE MARIA ARGUEDAS A</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.17933</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-76.97971</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1213,28 +1351,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>329790</t>
+          <t>329851</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7070 DRA. MARIA REICHE GROSSE NEUMAN</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>-12.16776</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-76.97257999999999</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1294</v>
-      </c>
-      <c r="J17" t="n">
-        <v>51</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+          <t>7099 HECTOR PRETELL / 7099 HECTOR PRETELL CARBONELL</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.17726</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-76.96907</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1260,28 +1408,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>329813</t>
+          <t>329969</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>7081 JOSE MARIA ARGUEDAS A</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>-12.17933</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-76.97971</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1288</v>
-      </c>
-      <c r="J18" t="n">
-        <v>60</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+          <t>JULIO CESAR ESCOBAR</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.16274</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-76.9744</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1307,28 +1465,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>329851</t>
+          <t>330171</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>7099 HECTOR PRETELL / 7099 HECTOR PRETELL CARBONELL</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>-12.17726</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-76.96907</v>
-      </c>
-      <c r="I19" t="n">
-        <v>646</v>
-      </c>
-      <c r="J19" t="n">
-        <v>30</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+          <t>FERMIN TANGUIS</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.1553</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-76.97698</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1354,28 +1522,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>329969</t>
+          <t>330208</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JULIO CESAR ESCOBAR</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>-12.16274</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-76.9744</v>
-      </c>
-      <c r="I20" t="n">
-        <v>756</v>
-      </c>
-      <c r="J20" t="n">
-        <v>44</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+          <t>ISAAC NEWTON</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.18218</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-76.97882</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1401,28 +1579,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>330171</t>
+          <t>330350</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FERMIN TANGUIS</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>-12.1553</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-76.97698</v>
-      </c>
-      <c r="I21" t="n">
-        <v>864</v>
-      </c>
-      <c r="J21" t="n">
-        <v>75</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+          <t>MARY'S CHILDREN SCHOOL</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.16094</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-76.96305</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1448,28 +1636,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>330208</t>
+          <t>331439</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ISAAC NEWTON</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>-12.18218</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-76.97882</v>
-      </c>
-      <c r="I22" t="n">
-        <v>339</v>
-      </c>
-      <c r="J22" t="n">
-        <v>21</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+          <t>AMERICA SIGLO XXI</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.18635</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-76.97633</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1495,28 +1693,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>330350</t>
+          <t>331694</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MARY'S CHILDREN SCHOOL</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>-12.16094</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-76.96305</v>
-      </c>
-      <c r="I23" t="n">
-        <v>179</v>
-      </c>
-      <c r="J23" t="n">
-        <v>6</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+          <t>HEROES DEL PACIFICO</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12.17175</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-76.96933</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1542,28 +1750,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>331439</t>
+          <t>332132</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AMERICA SIGLO XXI</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>-12.18635</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-76.97633</v>
-      </c>
-      <c r="I24" t="n">
-        <v>517</v>
-      </c>
-      <c r="J24" t="n">
-        <v>30</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+          <t>LEONARD EULER</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.16805</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-76.97689</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1589,122 +1807,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>331694</t>
+          <t>614443</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HEROES DEL PACIFICO</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>-12.17175</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-76.96933</v>
-      </c>
-      <c r="I25" t="n">
-        <v>370</v>
-      </c>
-      <c r="J25" t="n">
-        <v>24</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>150133</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE MIRAFLORES</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>332132</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>LEONARD EULER</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>-12.16805</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-76.97689</v>
-      </c>
-      <c r="I26" t="n">
-        <v>222</v>
-      </c>
-      <c r="J26" t="n">
-        <v>12</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>150133</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>SAN JUAN DE MIRAFLORES</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>614443</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
           <t>TALENTOS KIDS</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-12.17971</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-76.98159</v>
-      </c>
-      <c r="I27" t="n">
-        <v>193</v>
-      </c>
-      <c r="J27" t="n">
-        <v>11</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-12.17971</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-76.98159</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
